--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-05).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-05).xlsx
@@ -935,34 +935,34 @@
     <t>214</t>
   </si>
   <si>
-    <t>22</t>
+    <t>18</t>
   </si>
   <si>
-    <t>R$ 9.195,93</t>
+    <t>R$ 9.154,30</t>
   </si>
   <si>
-    <t>95.8</t>
+    <t>95.4</t>
   </si>
   <si>
-    <t>62.2</t>
+    <t>62.1</t>
   </si>
   <si>
-    <t>6.91</t>
+    <t>6.93</t>
   </si>
   <si>
-    <t>22.0</t>
+    <t>22.1</t>
   </si>
   <si>
-    <t>8.3</t>
+    <t>8.4</t>
   </si>
   <si>
     <t>6.4</t>
   </si>
   <si>
-    <t>30.6%</t>
+    <t>30.7%</t>
   </si>
   <si>
-    <t>17.0%</t>
+    <t>16.9%</t>
   </si>
   <si>
     <t>1.4%</t>
@@ -5019,7 +5019,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>51</v>
@@ -5049,14 +5049,26 @@
         <v>58</v>
       </c>
       <c r="L24" s="4"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="6"/>
+      <c r="M24" s="5">
+        <v>11648.91</v>
+      </c>
+      <c r="N24" s="6">
+        <v>132</v>
+      </c>
       <c r="O24" s="6"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
+      <c r="P24" s="7">
+        <v>7.4815384615384621</v>
+      </c>
+      <c r="Q24" s="8">
+        <v>29.572916346153843</v>
+      </c>
+      <c r="R24" s="8">
+        <v>15.422916346153848</v>
+      </c>
       <c r="S24" s="8"/>
-      <c r="T24" s="9"/>
+      <c r="T24" s="9">
+        <v>0.04807692307692308</v>
+      </c>
       <c r="U24" s="9"/>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -6843,7 +6855,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6873,14 +6885,26 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
+      <c r="M36" s="5">
+        <v>5356.8400000000001</v>
+      </c>
+      <c r="N36" s="6">
+        <v>65</v>
+      </c>
       <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
+      <c r="P36" s="7">
+        <v>4.8791000000000002</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>16.998638775510205</v>
+      </c>
+      <c r="R36" s="8">
+        <v>5.0639448979591837</v>
+      </c>
       <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
+      <c r="T36" s="9">
+        <v>0.34693877551020408</v>
+      </c>
       <c r="U36" s="9"/>
       <c r="V36" s="9"/>
       <c r="W36" s="9"/>
@@ -9132,7 +9156,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9162,14 +9186,26 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>707.22000000000003</v>
+      </c>
+      <c r="N51" s="6">
+        <v>8</v>
+      </c>
       <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
+      <c r="P51" s="7">
+        <v>5.6916624999999996</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>24.883299999999998</v>
+      </c>
+      <c r="R51" s="8">
+        <v>7.6333000000000002</v>
+      </c>
       <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
+      <c r="T51" s="9">
+        <v>0</v>
+      </c>
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
@@ -14834,7 +14870,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14862,14 +14898,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>10910.9</v>
+      </c>
+      <c r="N89" s="6">
+        <v>97</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>13.438605102040817</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>36.415666000000002</v>
+      </c>
+      <c r="R89" s="8">
+        <v>15.73333404255319</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0.059999999999999998</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
@@ -28548,7 +28596,9 @@
       <c r="N179" s="6">
         <v>117</v>
       </c>
-      <c r="O179" s="6"/>
+      <c r="O179" s="6">
+        <v>47</v>
+      </c>
       <c r="P179" s="7">
         <v>4.4562675213675211</v>
       </c>
@@ -28558,31 +28608,75 @@
       <c r="R179" s="8">
         <v>2.6039000000000003</v>
       </c>
-      <c r="S179" s="8"/>
+      <c r="S179" s="8">
+        <v>7</v>
+      </c>
       <c r="T179" s="9">
         <v>0.7021276595744681</v>
       </c>
-      <c r="U179" s="9"/>
-      <c r="V179" s="9"/>
-      <c r="W179" s="9"/>
-      <c r="X179" s="9"/>
-      <c r="Y179" s="9"/>
-      <c r="Z179" s="9"/>
-      <c r="AA179" s="9"/>
-      <c r="AB179" s="9"/>
-      <c r="AC179" s="9"/>
-      <c r="AD179" s="6"/>
-      <c r="AE179" s="6"/>
-      <c r="AF179" s="6"/>
-      <c r="AG179" s="6"/>
-      <c r="AH179" s="6"/>
-      <c r="AI179" s="6"/>
-      <c r="AJ179" s="6"/>
-      <c r="AK179" s="6"/>
-      <c r="AL179" s="6"/>
-      <c r="AM179" s="6"/>
-      <c r="AN179" s="9"/>
-      <c r="AO179" s="6"/>
+      <c r="U179" s="9">
+        <v>0</v>
+      </c>
+      <c r="V179" s="9">
+        <v>0</v>
+      </c>
+      <c r="W179" s="9">
+        <v>0</v>
+      </c>
+      <c r="X179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO179" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP179" s="4">
         <v>58</v>
       </c>
